--- a/MqSocial/10.2.0/angular/src/assets/templates/Danh sách KOL.xlsx
+++ b/MqSocial/10.2.0/angular/src/assets/templates/Danh sách KOL.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manhduongvan1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\manh-quan-media\mqmedia\MqSocial\10.2.0\angular\src\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD3B9E69-B669-4CEF-A9D6-4D268223DD8A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BF9B8E-9AF3-4706-B299-2F24175C0A23}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6636" xr2:uid="{B11E85F2-D84B-4805-8AE9-4CC0E0A96B62}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17250" windowHeight="6630" xr2:uid="{B11E85F2-D84B-4805-8AE9-4CC0E0A96B62}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>SĐT</t>
   </si>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t>Loại tài khoản</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Liên lạc</t>
   </si>
 </sst>
 </file>
@@ -536,18 +542,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A351BCD3-515F-4800-9A3B-3CAF1AE583BD}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.21875" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="21.88671875" customWidth="1"/>
-    <col min="5" max="5" width="26.44140625" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -566,8 +573,14 @@
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" s="11" customFormat="1">
+    <row r="2" spans="1:8" s="11" customFormat="1">
       <c r="A2" s="5"/>
       <c r="B2" s="6"/>
       <c r="C2" s="7"/>
@@ -589,7 +602,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DFE0985-DB7F-46EF-B16D-AF2BAE4DDEBA}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -613,7 +626,7 @@
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <titus xmlns="http://schemas.titus.com/TitusProperties/">
-  <TitusGUID xmlns="">b9f78278-8b89-401c-8cdd-ca994617c35d</TitusGUID>
+  <TitusGUID xmlns="">51fc0b37-ee86-42e8-bf27-4addf35a6d8c</TitusGUID>
   <TitusMetadata xmlns="">eyJucyI6Imh0dHA6XC9cL3d3dy50aXR1cy5jb21cL25zXC9BZ3JpYmFuayIsInByb3BzIjpbeyJuIjoiQ0xBU1NJRklDQVRJT04iLCJ2YWxzIjpbeyJ2YWx1ZSI6IlBVQkxJQyJ9XX1dfQ==</TitusMetadata>
 </titus>
 </file>
